--- a/data/trans_dic/P1435-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1435-Edad-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,1; 20,01</t>
+          <t>13,57; 19,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,9; 13,66</t>
+          <t>7,81; 13,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,23</t>
+          <t>3,48; 8,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 15,46</t>
+          <t>7,22; 16,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,1; 20,01</t>
+          <t>13,57; 19,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,9; 13,66</t>
+          <t>7,81; 13,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,23</t>
+          <t>3,48; 8,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 15,46</t>
+          <t>7,22; 16,9</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,26; 17,99</t>
+          <t>12,12; 17,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,15</t>
+          <t>4,27; 8,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,89</t>
+          <t>2,63; 5,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,69; 55,02</t>
+          <t>10,15; 16,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,26; 17,99</t>
+          <t>12,12; 17,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,15</t>
+          <t>4,27; 8,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,89</t>
+          <t>2,63; 5,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,69; 55,02</t>
+          <t>10,15; 16,66</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,79; 11,22</t>
+          <t>6,99; 11,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,46</t>
+          <t>4,78; 8,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,14</t>
+          <t>1,03; 3,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,63; 14,32</t>
+          <t>9,74; 14,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,79; 11,22</t>
+          <t>6,99; 11,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,46</t>
+          <t>4,78; 8,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,14</t>
+          <t>1,03; 3,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,63; 14,32</t>
+          <t>9,74; 14,31</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,49</t>
+          <t>2,19; 5,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,88</t>
+          <t>0,72; 3,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,75</t>
+          <t>0,75; 2,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,27</t>
+          <t>4,91; 7,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,49</t>
+          <t>2,19; 5,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,88</t>
+          <t>0,72; 3,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,75</t>
+          <t>0,75; 2,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,27</t>
+          <t>4,91; 7,76</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,97</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,08</t>
+          <t>0,11; 0,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,97</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,08</t>
+          <t>0,11; 0,96</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,3</t>
+          <t>0,26; 2,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,3</t>
+          <t>0,26; 2,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -1361,42 +1361,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,8; 8,61</t>
+          <t>6,84; 8,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,58</t>
+          <t>3,26; 4,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,39</t>
+          <t>1,46; 2,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,99</t>
+          <t>5,4; 6,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,8; 8,61</t>
+          <t>6,84; 8,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,58</t>
+          <t>3,26; 4,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,39</t>
+          <t>1,46; 2,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,99</t>
+          <t>5,4; 6,96</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30408</t>
+          <t>40891</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30408</t>
+          <t>40891</t>
         </is>
       </c>
     </row>
@@ -1635,42 +1635,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>61225; 93537</t>
+          <t>63461; 93329</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34004; 58752</t>
+          <t>33609; 59515</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14286; 32569</t>
+          <t>13789; 32129</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18216; 48406</t>
+          <t>26185; 61250</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>61225; 93537</t>
+          <t>63461; 93329</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34004; 58752</t>
+          <t>33609; 59515</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14286; 32569</t>
+          <t>13789; 32129</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18216; 48406</t>
+          <t>26185; 61250</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>129788</t>
+          <t>66455</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>129788</t>
+          <t>66455</t>
         </is>
       </c>
     </row>
@@ -1783,42 +1783,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76663; 112505</t>
+          <t>75784; 111759</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25568; 49729</t>
+          <t>26038; 49631</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14199; 33190</t>
+          <t>14846; 33458</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64765; 280695</t>
+          <t>50592; 83040</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76663; 112505</t>
+          <t>75784; 111759</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25568; 49729</t>
+          <t>26038; 49631</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14199; 33190</t>
+          <t>14846; 33458</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64765; 280695</t>
+          <t>50592; 83040</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63375</t>
+          <t>73176</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63375</t>
+          <t>73176</t>
         </is>
       </c>
     </row>
@@ -1931,42 +1931,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46828; 77422</t>
+          <t>48190; 77202</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33125; 60050</t>
+          <t>33896; 62651</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5918; 20789</t>
+          <t>6818; 20651</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51861; 77127</t>
+          <t>60238; 88458</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46828; 77422</t>
+          <t>48190; 77202</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33125; 60050</t>
+          <t>33896; 62651</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5918; 20789</t>
+          <t>6818; 20651</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51861; 77127</t>
+          <t>60238; 88458</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41050</t>
+          <t>46073</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41050</t>
+          <t>46073</t>
         </is>
       </c>
     </row>
@@ -2079,42 +2079,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11673; 28313</t>
+          <t>11301; 27800</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4421; 17672</t>
+          <t>4440; 19026</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5099; 17864</t>
+          <t>4845; 17609</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31660; 51682</t>
+          <t>36105; 57040</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11673; 28313</t>
+          <t>11301; 27800</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4421; 17672</t>
+          <t>4440; 19026</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5099; 17864</t>
+          <t>4845; 17609</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31660; 51682</t>
+          <t>36105; 57040</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2338</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>792; 7962</t>
+          <t>0; 8078</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>589; 5909</t>
+          <t>679; 5841</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>792; 7962</t>
+          <t>0; 8078</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>589; 5909</t>
+          <t>679; 5841</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>874; 7892</t>
+          <t>884; 8151</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>874; 7892</t>
+          <t>884; 8151</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 8269</t>
+          <t>0; 7616</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 8269</t>
+          <t>0; 7616</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
     </row>
@@ -2671,42 +2671,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>229865; 290809</t>
+          <t>231258; 290641</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>116982; 162900</t>
+          <t>115776; 162178</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>52831; 84756</t>
+          <t>51767; 83952</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>188999; 510642</t>
+          <t>201079; 259341</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>229865; 290809</t>
+          <t>231258; 290641</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>116982; 162900</t>
+          <t>115776; 162178</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>52831; 84756</t>
+          <t>51767; 83952</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>188999; 510642</t>
+          <t>201079; 259341</t>
         </is>
       </c>
     </row>
